--- a/docs/royalty-fee-template-apis.xlsx
+++ b/docs/royalty-fee-template-apis.xlsx
@@ -300,63 +300,91 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.25" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26.25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26.25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="21.25" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="31.25" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="40" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>TIN</x:v>
+      <x:c r="A1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>TIN</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>Date_Investment_License</x:v>
+      <x:c r="B1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Date_Investment_License</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>Electricity_sale_value</x:v>
+      <x:c r="C1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Electricity_sale_value</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>Royalty_fee_rate</x:v>
+      <x:c r="D1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Royalty_fee_rate</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>Royalty_fee_collected</x:v>
+      <x:c r="E1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Royalty_fee_collected</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>Year_data</x:v>
+      <x:c r="F1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Year_data</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>Use User Fallback?</x:v>
+      <x:c r="G1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback?</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>User Benchmark Rate</x:v>
+      <x:c r="H1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User Benchmark Rate</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I1" s="6" t="str">
-        <x:v>User Benchmark Fee</x:v>
+      <x:c r="I1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User Benchmark Fee</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J1" s="6" t="str">
-        <x:v>User TE</x:v>
+      <x:c r="J1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User TE</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K1" s="6" t="str">
-        <x:v>User Fallback Reason</x:v>
+      <x:c r="K1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback Reason</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L1" s="6" t="str">
-        <x:v>User Comment</x:v>
+      <x:c r="L1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>User Comment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="15" t="str">
-        <x:v>123456789-000</x:v>
+      <x:c r="A2" s="15" t="inlineStr">
+        <x:is>
+          <x:t>123456789-000</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B2" s="16" t="str">
-        <x:v>2026-01-01</x:v>
+      <x:c r="B2" s="16" t="inlineStr">
+        <x:is>
+          <x:t>2026-01-01</x:t>
+        </x:is>
       </x:c>
       <x:c r="C2" s="17" t="n">
         <x:v>100000000</x:v>
@@ -370,14 +398,16 @@
       <x:c r="F2" s="19" t="n">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="G2" s="15" t="str">
-        <x:v>No</x:v>
+      <x:c r="G2" s="15" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
       </x:c>
       <x:c r="H2" s="18"/>
       <x:c r="I2" s="17"/>
       <x:c r="J2" s="17"/>
-      <x:c r="K2" s="15" t="str"/>
-      <x:c r="L2" s="15" t="str"/>
+      <x:c r="K2" s="15"/>
+      <x:c r="L2" s="15"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5"/>
@@ -14366,7 +14396,6 @@
       <x:c r="L1001" s="8"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:dataValidations count="4">
     <x:dataValidation type="whole" operator="between" allowBlank="0" showErrorMessage="1" sqref="F2:F1001">
       <x:formula1>2000</x:formula1>
@@ -14382,6 +14411,7 @@
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -14396,207 +14426,299 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="str">
-        <x:v>Royalty Fee Import Template - Instructions</x:v>
+      <x:c r="A1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Royalty Fee Import Template - Instructions</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="27" t="str">
-        <x:v>Information Type</x:v>
+      <x:c r="A3" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Information Type</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B3" s="27" t="str">
-        <x:v>Color</x:v>
+      <x:c r="B3" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Color</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C3" s="27" t="str">
-        <x:v>Meaning</x:v>
+      <x:c r="C3" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Meaning</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D3" s="27" t="str">
-        <x:v>Examples</x:v>
+      <x:c r="D3" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Examples</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="5" t="str">
-        <x:v>Primary Required</x:v>
+      <x:c r="A4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Primary Required</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B4" s="5" t="str">
-        <x:v>Dark blue header, light blue input cells</x:v>
+      <x:c r="B4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue header, light blue input cells</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C4" s="5" t="str">
-        <x:v>Required for normal royalty fee TE calculation.</x:v>
+      <x:c r="C4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Required for normal royalty fee TE calculation.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D4" s="5" t="str">
-        <x:v>TIN, electricity sale value, actual rate, collected fee, year</x:v>
+      <x:c r="D4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>TIN, electricity sale value, actual rate, collected fee, year</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="25" t="str">
-        <x:v>Primary Optional</x:v>
+      <x:c r="A5" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Primary Optional</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B5" s="25" t="str">
-        <x:v>Dark blue header, light blue cells</x:v>
+      <x:c r="B5" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue header, light blue cells</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C5" s="25" t="str">
-        <x:v>Useful for audit but not always required for calculation.</x:v>
+      <x:c r="C5" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Useful for audit but not always required for calculation.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D5" s="25" t="str">
-        <x:v>Date Investment License</x:v>
+      <x:c r="D5" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Date Investment License</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="8" t="str">
-        <x:v>User Fallback</x:v>
+      <x:c r="A6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>Orange header, light amber input cells</x:v>
+      <x:c r="B6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Orange header, light amber input cells</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C6" s="8" t="str">
-        <x:v>Optional user-provided benchmark or TE value used only when normal system calculation is insufficient.</x:v>
+      <x:c r="C6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Optional user-provided benchmark or TE value used only when normal system calculation is insufficient.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D6" s="8" t="str">
-        <x:v>User Benchmark Rate, User Benchmark Fee, User TE</x:v>
+      <x:c r="D6" s="8" t="inlineStr">
+        <x:is>
+          <x:t>User Benchmark Rate, User Benchmark Fee, User TE</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="25" t="str">
-        <x:v>Protected Reference Sheets</x:v>
+      <x:c r="A7" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Protected Reference Sheets</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B7" s="25" t="str">
-        <x:v>Dark blue headers</x:v>
+      <x:c r="B7" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue headers</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C7" s="25" t="str">
-        <x:v>Instructions, Validation Lists, and Data Dictionary are read-only.</x:v>
+      <x:c r="C7" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Instructions, Validation Lists, and Data Dictionary are read-only.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D7" s="25" t="str">
-        <x:v>Use Royalty Fee Import for data entry.</x:v>
+      <x:c r="D7" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Use Royalty Fee Import for data entry.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="25" t="str"/>
-      <x:c r="B8" s="25" t="str"/>
-      <x:c r="C8" s="25" t="str"/>
-      <x:c r="D8" s="25" t="str"/>
+      <x:c r="A8" s="25"/>
+      <x:c r="B8" s="25"/>
+      <x:c r="C8" s="25"/>
+      <x:c r="D8" s="25"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="25" t="str">
-        <x:v>Rule</x:v>
+      <x:c r="A9" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Rule</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B9" s="25" t="str">
-        <x:v>Description</x:v>
+      <x:c r="B9" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C9" s="25" t="str"/>
-      <x:c r="D9" s="25" t="str"/>
+      <x:c r="C9" s="25"/>
+      <x:c r="D9" s="25"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="27" t="str">
-        <x:v>Current compatibility</x:v>
+      <x:c r="A10" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Current compatibility</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B10" s="27" t="str">
-        <x:v>Columns A:F match the current Royalty Fee importer.</x:v>
+      <x:c r="B10" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Columns A:F match the current Royalty Fee importer.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C10" s="27" t="str"/>
-      <x:c r="D10" s="27" t="str"/>
+      <x:c r="C10" s="27"/>
+      <x:c r="D10" s="27"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="25" t="str">
-        <x:v>Use primary first</x:v>
+      <x:c r="A11" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Use primary first</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B11" s="25" t="str">
-        <x:v>The system uses Year_data to find the official royalty benchmark rate, then calculates benchmark fee from Electricity_sale_value.</x:v>
+      <x:c r="B11" s="25" t="inlineStr">
+        <x:is>
+          <x:t>The system uses Year_data to find the official royalty benchmark rate, then calculates benchmark fee from Electricity_sale_value.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C11" s="25" t="str"/>
-      <x:c r="D11" s="25" t="str"/>
+      <x:c r="C11" s="25"/>
+      <x:c r="D11" s="25"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="25" t="str">
-        <x:v>No simple Excel calculations</x:v>
+      <x:c r="A12" s="25" t="inlineStr">
+        <x:is>
+          <x:t>No simple Excel calculations</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B12" s="25" t="str">
-        <x:v>Do not add Excel-calculated TE columns for simple rate math. The system should calculate benchmark fee and TE.</x:v>
+      <x:c r="B12" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Do not add Excel-calculated TE columns for simple rate math. The system should calculate benchmark fee and TE.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C12" s="25" t="str"/>
-      <x:c r="D12" s="25" t="str"/>
+      <x:c r="C12" s="25"/>
+      <x:c r="D12" s="25"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="25" t="str">
-        <x:v>Benchmark repository warning</x:v>
+      <x:c r="A13" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark repository warning</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B13" s="25" t="str">
-        <x:v>The local bm_royalty_fees table is currently empty. It must be populated before calculation will succeed.</x:v>
+      <x:c r="B13" s="25" t="inlineStr">
+        <x:is>
+          <x:t>The local bm_royalty_fees table is currently empty. It must be populated before calculation will succeed.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C13" s="25" t="str"/>
-      <x:c r="D13" s="25" t="str"/>
+      <x:c r="C13" s="25"/>
+      <x:c r="D13" s="25"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="25" t="str">
-        <x:v>Hybrid fallback</x:v>
+      <x:c r="A14" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Hybrid fallback</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B14" s="25" t="str">
-        <x:v>Use User Fallback fields only when the official benchmark is missing, disputed, or a user-agreed value must be documented.</x:v>
+      <x:c r="B14" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback fields only when the official benchmark is missing, disputed, or a user-agreed value must be documented.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C14" s="25" t="str"/>
-      <x:c r="D14" s="25" t="str"/>
+      <x:c r="C14" s="25"/>
+      <x:c r="D14" s="25"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="25" t="str">
-        <x:v>Mandatory fields</x:v>
+      <x:c r="A15" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Mandatory fields</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B15" s="25" t="str">
-        <x:v>TIN, Electricity_sale_value, Royalty_fee_rate, Royalty_fee_collected, and Year_data.</x:v>
+      <x:c r="B15" s="25" t="inlineStr">
+        <x:is>
+          <x:t>TIN, Electricity_sale_value, Royalty_fee_rate, Royalty_fee_collected, and Year_data.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C15" s="25" t="str"/>
-      <x:c r="D15" s="25" t="str"/>
+      <x:c r="C15" s="25"/>
+      <x:c r="D15" s="25"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="25" t="str">
-        <x:v>Calculation note</x:v>
+      <x:c r="A16" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Calculation note</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B16" s="25" t="str">
-        <x:v>System benchmark fee = Electricity_sale_value x benchmark rate. TE = max(benchmark fee - collected fee, 0).</x:v>
+      <x:c r="B16" s="25" t="inlineStr">
+        <x:is>
+          <x:t>System benchmark fee = Electricity_sale_value x benchmark rate. TE = max(benchmark fee - collected fee, 0).</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C16" s="25" t="str"/>
-      <x:c r="D16" s="25" t="str"/>
+      <x:c r="C16" s="25"/>
+      <x:c r="D16" s="25"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="25" t="str">
-        <x:v>Template version</x:v>
+      <x:c r="A17" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Template version</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B17" s="25" t="str">
-        <x:v>ROYALTY_FEE_IMPORT v1.0</x:v>
+      <x:c r="B17" s="25" t="inlineStr">
+        <x:is>
+          <x:t>ROYALTY_FEE_IMPORT v1.0</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C17" s="25" t="str"/>
-      <x:c r="D17" s="25" t="str"/>
+      <x:c r="C17" s="25"/>
+      <x:c r="D17" s="25"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="25" t="str">
-        <x:v>Protection password</x:v>
+      <x:c r="A18" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Protection password</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B18" s="25" t="str">
-        <x:v>TaxETS2026</x:v>
+      <x:c r="B18" s="25" t="inlineStr">
+        <x:is>
+          <x:t>TaxETS2026</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C18" s="25" t="str">
-        <x:v>Used only to prevent accidental edits to read-only sheets.</x:v>
+      <x:c r="C18" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Used only to prevent accidental edits to read-only sheets.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D18" s="25" t="str"/>
+      <x:c r="D18" s="25"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="25" t="str">
-        <x:v>Import code note</x:v>
+      <x:c r="A19" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Import code note</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B19" s="25" t="str">
-        <x:v>Current importer reads only A:F. Fallback columns G:L are discussion fields until import logic is extended.</x:v>
+      <x:c r="B19" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Current importer reads only A:F. Fallback columns G:L are discussion fields until import logic is extended.</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C19" s="25" t="str"/>
-      <x:c r="D19" s="25" t="str"/>
+      <x:c r="C19" s="25"/>
+      <x:c r="D19" s="25"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="25" t="str">
-        <x:v>Benchmark source</x:v>
+      <x:c r="A20" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark source</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B20" s="25" t="str">
-        <x:v>Fallback discussion row because local bm_royalty_fees is empty</x:v>
+      <x:c r="B20" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Fallback discussion row because local bm_royalty_fees is empty</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C20" s="25" t="str"/>
-      <x:c r="D20" s="25" t="str"/>
+      <x:c r="C20" s="25"/>
+      <x:c r="D20" s="25"/>
     </x:row>
   </x:sheetData>
   <x:sheetProtection password="C3BC" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -14614,80 +14736,116 @@
     <x:col min="1" max="1" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="45" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="45" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="45" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="18.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="45" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="45" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="45" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="21" t="str">
-        <x:v>Yes/No</x:v>
+      <x:c r="A1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Yes/No</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B1" s="21" t="str"/>
-      <x:c r="C1" s="21" t="str">
-        <x:v>Fallback Reason</x:v>
+      <x:c r="B1" s="21"/>
+      <x:c r="C1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Fallback Reason</x:t>
+        </x:is>
       </x:c>
       <x:c r="D1" s="21"/>
-      <x:c r="E1" s="21" t="str">
-        <x:v>Provision Code</x:v>
+      <x:c r="E1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Provision Code</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F1" s="21" t="str">
-        <x:v>Provision Name</x:v>
+      <x:c r="F1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Provision Name</x:t>
+        </x:is>
       </x:c>
-      <x:c r="G1" s="21" t="str">
-        <x:v>Benchmark Rate %</x:v>
+      <x:c r="G1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark Rate %</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H1" s="21" t="str">
-        <x:v>Start Year</x:v>
+      <x:c r="H1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Start Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I1" s="21" t="str">
-        <x:v>End Year</x:v>
+      <x:c r="I1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>End Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J1" s="21" t="str">
-        <x:v>Note</x:v>
+      <x:c r="J1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Note</x:t>
+        </x:is>
       </x:c>
       <x:c r="K1" s="21"/>
-      <x:c r="L1" s="21" t="str">
-        <x:v>Provision Code</x:v>
+      <x:c r="L1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Provision Code</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M1" s="21" t="str">
-        <x:v>Provision Name</x:v>
+      <x:c r="M1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Provision Name</x:t>
+        </x:is>
       </x:c>
-      <x:c r="N1" s="21" t="str">
-        <x:v>Category</x:v>
+      <x:c r="N1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Category</x:t>
+        </x:is>
       </x:c>
-      <x:c r="O1" s="21" t="str">
-        <x:v>Exemption Years</x:v>
+      <x:c r="O1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Exemption Years</x:t>
+        </x:is>
       </x:c>
-      <x:c r="P1" s="21" t="str">
-        <x:v>Reduction %</x:v>
+      <x:c r="P1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Reduction %</x:t>
+        </x:is>
       </x:c>
-      <x:c r="Q1" s="21" t="str">
-        <x:v>Period</x:v>
+      <x:c r="Q1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Period</x:t>
+        </x:is>
       </x:c>
-      <x:c r="R1" s="21" t="str">
-        <x:v>Description</x:v>
+      <x:c r="R1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>No</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C2" t="str"/>
-      <x:c r="E2" t="str">
-        <x:v>70</x:v>
+      <x:c r="C2"/>
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t>70</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F2" t="str">
-        <x:v>6.1 Royalty Fees</x:v>
+      <x:c r="F2" t="inlineStr">
+        <x:is>
+          <x:t>6.1 Royalty Fees</x:t>
+        </x:is>
       </x:c>
       <x:c r="G2" t="n">
         <x:v>10</x:v>
@@ -14698,67 +14856,95 @@
       <x:c r="I2" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="J2" t="str">
-        <x:v>Discussion fallback row - confirm official benchmark rate</x:v>
+      <x:c r="J2" t="inlineStr">
+        <x:is>
+          <x:t>Discussion fallback row - confirm official benchmark rate</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L2" t="str">
-        <x:v>70</x:v>
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>70</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M2" t="str">
-        <x:v>6.1 Royalty Fees</x:v>
+      <x:c r="M2" t="inlineStr">
+        <x:is>
+          <x:t>6.1 Royalty Fees</x:t>
+        </x:is>
       </x:c>
-      <x:c r="N2" t="str">
-        <x:v>Royalty Fee</x:v>
+      <x:c r="N2" t="inlineStr">
+        <x:is>
+          <x:t>Royalty Fee</x:t>
+        </x:is>
       </x:c>
       <x:c r="O2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P2" t="str">
-        <x:v>0.00</x:v>
+      <x:c r="P2" t="inlineStr">
+        <x:is>
+          <x:t>0.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="Q2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R2" t="str">
-        <x:v>6.1 Royalty Fees</x:v>
+      <x:c r="R2" t="inlineStr">
+        <x:is>
+          <x:t>6.1 Royalty Fees</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>Yes</x:v>
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Missing royalty benchmark rate</x:v>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t>Missing royalty benchmark rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="C4" t="str">
-        <x:v>Benchmark rate not officially confirmed</x:v>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark rate not officially confirmed</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="C5" t="str">
-        <x:v>Special legal treatment</x:v>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t>Special legal treatment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="C6" t="str">
-        <x:v>Legacy assessment</x:v>
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t>Legacy assessment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="C7" t="str">
-        <x:v>User judgment</x:v>
+      <x:c r="C7" t="inlineStr">
+        <x:is>
+          <x:t>User judgment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="C8" t="str">
-        <x:v>Other</x:v>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t>Other</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="C9" t="str">
-        <x:v>To be confirmed</x:v>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>To be confirmed</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14772,68 +14958,98 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="47.5" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="47.5" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="47.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="18.75" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="47.5" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="47.5" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="47.5" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="47.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
-        <x:v>Provision Code</x:v>
+      <x:c r="A1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Provision Code</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B1" s="23" t="str">
-        <x:v>Provision Name</x:v>
+      <x:c r="B1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Provision Name</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C1" s="23" t="str">
-        <x:v>Benchmark Rate %</x:v>
+      <x:c r="C1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark Rate %</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D1" s="23" t="str">
-        <x:v>Start Year</x:v>
+      <x:c r="D1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Start Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="E1" s="23" t="str">
-        <x:v>End Year</x:v>
+      <x:c r="E1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>End Year</x:t>
+        </x:is>
       </x:c>
-      <x:c r="F1" s="23" t="str">
-        <x:v>Source / Note</x:v>
+      <x:c r="F1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Source / Note</x:t>
+        </x:is>
       </x:c>
       <x:c r="G1" s="23"/>
-      <x:c r="H1" s="23" t="str">
-        <x:v>Provision Code</x:v>
+      <x:c r="H1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Provision Code</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I1" s="23" t="str">
-        <x:v>Provision Name</x:v>
+      <x:c r="I1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Provision Name</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J1" s="23" t="str">
-        <x:v>Category</x:v>
+      <x:c r="J1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Category</x:t>
+        </x:is>
       </x:c>
-      <x:c r="K1" s="23" t="str">
-        <x:v>Exemption Years</x:v>
+      <x:c r="K1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Exemption Years</x:t>
+        </x:is>
       </x:c>
-      <x:c r="L1" s="23" t="str">
-        <x:v>Reduction %</x:v>
+      <x:c r="L1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Reduction %</x:t>
+        </x:is>
       </x:c>
-      <x:c r="M1" s="23" t="str">
-        <x:v>Period</x:v>
+      <x:c r="M1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Period</x:t>
+        </x:is>
       </x:c>
-      <x:c r="N1" s="23" t="str">
-        <x:v>Description</x:v>
+      <x:c r="N1" s="23" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>70</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t>70</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B2" t="str">
-        <x:v>6.1 Royalty Fees</x:v>
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t>6.1 Royalty Fees</x:t>
+        </x:is>
       </x:c>
       <x:c r="C2" t="n">
         <x:v>10</x:v>
@@ -14844,42 +15060,58 @@
       <x:c r="E2" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="F2" t="str">
-        <x:v>Discussion fallback row - confirm official benchmark rate</x:v>
+      <x:c r="F2" t="inlineStr">
+        <x:is>
+          <x:t>Discussion fallback row - confirm official benchmark rate</x:t>
+        </x:is>
       </x:c>
-      <x:c r="H2" t="str">
-        <x:v>70</x:v>
+      <x:c r="H2" t="inlineStr">
+        <x:is>
+          <x:t>70</x:t>
+        </x:is>
       </x:c>
-      <x:c r="I2" t="str">
-        <x:v>6.1 Royalty Fees</x:v>
+      <x:c r="I2" t="inlineStr">
+        <x:is>
+          <x:t>6.1 Royalty Fees</x:t>
+        </x:is>
       </x:c>
-      <x:c r="J2" t="str">
-        <x:v>Royalty Fee</x:v>
+      <x:c r="J2" t="inlineStr">
+        <x:is>
+          <x:t>Royalty Fee</x:t>
+        </x:is>
       </x:c>
       <x:c r="K2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L2" t="str">
-        <x:v>0.00</x:v>
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>0.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="M2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N2" t="str">
-        <x:v>6.1 Royalty Fees</x:v>
+      <x:c r="N2" t="inlineStr">
+        <x:is>
+          <x:t>6.1 Royalty Fees</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="7" t="str">
-        <x:v>Benchmark source</x:v>
+      <x:c r="A5" s="7" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark source</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B5" s="7" t="str">
-        <x:v>Fallback discussion row because local bm_royalty_fees is empty</x:v>
+      <x:c r="B5" s="7" t="inlineStr">
+        <x:is>
+          <x:t>Fallback discussion row because local bm_royalty_fees is empty</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C5" s="7" t="str"/>
-      <x:c r="D5" s="7" t="str"/>
-      <x:c r="E5" s="7" t="str"/>
-      <x:c r="F5" s="7" t="str"/>
+      <x:c r="C5" s="7"/>
+      <x:c r="D5" s="7"/>
+      <x:c r="E5" s="7"/>
+      <x:c r="F5" s="7"/>
     </x:row>
   </x:sheetData>
   <x:sheetProtection password="C3BC" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -14898,31 +15130,47 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="28" t="str">
-        <x:v>Version</x:v>
+      <x:c r="A1" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Version</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B1" s="28" t="str">
-        <x:v>Date</x:v>
+      <x:c r="B1" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Date</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C1" s="28" t="str">
-        <x:v>Owner</x:v>
+      <x:c r="C1" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Owner</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D1" s="28" t="str">
-        <x:v>Change</x:v>
+      <x:c r="D1" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Change</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="25" t="str">
-        <x:v>1.0</x:v>
+      <x:c r="A2" s="25" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
       </x:c>
-      <x:c r="B2" s="25" t="str">
-        <x:v>2026-06-05</x:v>
+      <x:c r="B2" s="25" t="inlineStr">
+        <x:is>
+          <x:t>2026-06-05</x:t>
+        </x:is>
       </x:c>
-      <x:c r="C2" s="25" t="str">
-        <x:v>APIS / Tax-ETS</x:v>
+      <x:c r="C2" s="25" t="inlineStr">
+        <x:is>
+          <x:t>APIS / Tax-ETS</x:t>
+        </x:is>
       </x:c>
-      <x:c r="D2" s="25" t="str">
-        <x:v>Initial recommended Royalty Fee template with compatible A:F and user fallback G:L.</x:v>
+      <x:c r="D2" s="25" t="inlineStr">
+        <x:is>
+          <x:t>Initial recommended Royalty Fee template with compatible A:F and user fallback G:L.</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
